--- a/BugReport/Bug_Report_Playwright.xlsx
+++ b/BugReport/Bug_Report_Playwright.xlsx
@@ -997,6 +997,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>